--- a/data/pharmacology/WT_cAMP_vs_TRUPATH_All_Drugs.xlsx
+++ b/data/pharmacology/WT_cAMP_vs_TRUPATH_All_Drugs.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002F4F4F"/>
-        <bgColor rgb="002F4F4F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F9F9F9"/>
-        <bgColor rgb="00F9F9F9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,41 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D3D3D3"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D3D3D3"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D3D3D3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D3D3D3"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,193 +415,188 @@
   </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Ligand</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>cAMP Response</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>TRUPATH (Gi1)</t>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TRUPATH_Gi1_Emax_pct_DAMGO</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cAMP_response_raw</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>DAMGO</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" t="n">
         <v>100</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="n">
         <v>-0.6159</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>PZM21</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" t="n">
         <v>78.72</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
         <v>-0.5987</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Methadone</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" t="n">
         <v>83.33</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" t="n">
         <v>-0.5685</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Naloxone</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" t="n">
         <v>14.88</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" t="n">
         <v>-0.1303</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Carfentanil</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" t="n">
         <v>97.15000000000001</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" t="n">
         <v>-0.6348</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Morphine</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" t="n">
         <v>98.77</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" t="n">
         <v>-0.5492</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Nalbuphine</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" t="n">
         <v>46.96</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" t="n">
         <v>-0.4038</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Butorphanol</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" t="n">
         <v>64.81</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" t="n">
         <v>-0.4571</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Buprenorphine</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
+      <c r="B10" t="n">
         <v>60.18</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" t="n">
         <v>-0.2713</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>C6Guano</t>
         </is>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" t="n">
         <v>88.31999999999999</v>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>TRV130</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
+      <c r="B12" t="n">
         <v>77.20999999999999</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" t="n">
         <v>-0.6347</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" t="n">
         <v>65.92</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" t="n">
         <v>-0.578</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Fentanyl</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" t="n">
         <v>96.39</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" t="n">
         <v>-0.6113</v>
       </c>
     </row>
